--- a/artfynd/A 14646-2023 artfynd.xlsx
+++ b/artfynd/A 14646-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14646-2023 artfynd.xlsx
+++ b/artfynd/A 14646-2023 artfynd.xlsx
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5986845</v>
+        <v>5772221</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>223246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584799.3468137302</v>
+        <v>584799</v>
       </c>
       <c r="R2" t="n">
-        <v>6498436.577630339</v>
+        <v>6498437</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +743,9 @@
           <t>2012-06-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6353499</v>
+        <v>5986845</v>
       </c>
       <c r="B3" t="n">
-        <v>98932</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224932</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -824,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584799.3468137302</v>
+        <v>584799</v>
       </c>
       <c r="R3" t="n">
-        <v>6498436.577630339</v>
+        <v>6498437</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -857,19 +841,9 @@
           <t>2012-06-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +875,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5772221</v>
+        <v>6353499</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>224932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vanlig backsmörblomma</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584799.3468137302</v>
+        <v>584799</v>
       </c>
       <c r="R4" t="n">
-        <v>6498436.577630339</v>
+        <v>6498437</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -974,19 +939,9 @@
           <t>2012-06-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 14646-2023 artfynd.xlsx
+++ b/artfynd/A 14646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5772221</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5986845</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,8 +985,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6353499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>